--- a/ActionGame-リファクタリング-/Data/CSV/Boss/AttackPatterns/AttackPatterns.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Boss/AttackPatterns/AttackPatterns.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\FindWorkProject\ActionGame-リファクタリング-\Data\CSV\Boss\AttackPatterns\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Boss\AttackPatterns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BB6E32-8D62-481B-AD94-BA347B461678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E21AB95-45C5-4CB2-9255-B9B3C8C889F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{59E832E3-1EA6-4DA0-B38C-FAE5464E904C}"/>
+    <workbookView xWindow="-5715" yWindow="4215" windowWidth="21600" windowHeight="11295" xr2:uid="{59E832E3-1EA6-4DA0-B38C-FAE5464E904C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -392,25 +392,128 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56D5B0E-6B3B-4C32-9CF0-D1F97C4E45FB}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="7" width="3.625" customWidth="1"/>
     <col min="8" max="8" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B1">
-        <v>14</v>
+        <v>5</v>
+      </c>
+      <c r="C1">
+        <v>6</v>
+      </c>
+      <c r="D1">
+        <v>5</v>
+      </c>
+      <c r="E1">
+        <v>7</v>
+      </c>
+      <c r="F1">
+        <v>8</v>
+      </c>
+      <c r="G1">
+        <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="5" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ActionGame-リファクタリング-/Data/CSV/Boss/AttackPatterns/AttackPatterns.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Boss/AttackPatterns/AttackPatterns.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Boss\AttackPatterns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E21AB95-45C5-4CB2-9255-B9B3C8C889F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B8831D-AE71-4CD5-AABD-3FB52091CEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5715" yWindow="4215" windowWidth="21600" windowHeight="11295" xr2:uid="{59E832E3-1EA6-4DA0-B38C-FAE5464E904C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{59E832E3-1EA6-4DA0-B38C-FAE5464E904C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ActionGame-リファクタリング-/Data/CSV/Boss/AttackPatterns/AttackPatterns.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Boss/AttackPatterns/AttackPatterns.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Boss\AttackPatterns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B8831D-AE71-4CD5-AABD-3FB52091CEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B680F3D-3824-4116-A0B1-319C5EB18D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{59E832E3-1EA6-4DA0-B38C-FAE5464E904C}"/>
+    <workbookView xWindow="2955" yWindow="3030" windowWidth="21600" windowHeight="11295" xr2:uid="{59E832E3-1EA6-4DA0-B38C-FAE5464E904C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ActionGame-リファクタリング-/Data/CSV/Boss/AttackPatterns/AttackPatterns.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Boss/AttackPatterns/AttackPatterns.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Boss\AttackPatterns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B680F3D-3824-4116-A0B1-319C5EB18D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92D95FB-6493-48A3-8CA9-E982C11F35C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2955" yWindow="3030" windowWidth="21600" windowHeight="11295" xr2:uid="{59E832E3-1EA6-4DA0-B38C-FAE5464E904C}"/>
+    <workbookView xWindow="5340" yWindow="1440" windowWidth="21600" windowHeight="11295" xr2:uid="{59E832E3-1EA6-4DA0-B38C-FAE5464E904C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -424,13 +424,13 @@
     </row>
     <row r="2" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -447,13 +447,13 @@
     </row>
     <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -470,13 +470,13 @@
     </row>
     <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -493,25 +493,25 @@
     </row>
     <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
         <v>7</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>8</v>
       </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
       <c r="G5">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
